--- a/outputs/daily/hr_rankings_2026-07-21.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-21.xlsx
@@ -63747,12 +63747,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>691011</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Drew Romo</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -63796,7 +63796,7 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -63810,14 +63810,14 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P231" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="Q231" t="n">
-        <v>47.5</v>
+        <v>48.8</v>
       </c>
       <c r="R231" t="n">
         <v>27.6</v>
@@ -63826,10 +63826,10 @@
         <v>47.9</v>
       </c>
       <c r="T231" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U231" t="n">
-        <v>0</v>
+        <v>38.3</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -63885,12 +63885,12 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
@@ -63900,12 +63900,12 @@
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Contact streak: 9/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.9% barrel, 11.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 11.7 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
@@ -63915,67 +63915,67 @@
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>95.6315</t>
+          <t>97.4384</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.2023</t>
+          <t>0.3253</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.0805</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.1736</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>68.42</t>
+          <t>67.12</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.1253</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
@@ -66231,12 +66231,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>691011</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Drew Romo</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -66280,7 +66280,7 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
@@ -66294,14 +66294,14 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P240" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="Q240" t="n">
-        <v>48.8</v>
+        <v>47.5</v>
       </c>
       <c r="R240" t="n">
         <v>27.6</v>
@@ -66310,10 +66310,10 @@
         <v>40.2</v>
       </c>
       <c r="T240" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U240" t="n">
-        <v>38.3</v>
+        <v>0</v>
       </c>
       <c r="V240" t="inlineStr">
         <is>
@@ -66369,12 +66369,12 @@
       </c>
       <c r="AH240" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI240" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ240" t="inlineStr">
@@ -66384,12 +66384,12 @@
       </c>
       <c r="AK240" t="inlineStr">
         <is>
-          <t>Contact streak: 9/24 over last 7 games</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL240" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 11.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.9% barrel, 11.7 HR allowed</t>
         </is>
       </c>
       <c r="AM240" t="inlineStr">
@@ -66399,67 +66399,67 @@
       </c>
       <c r="AN240" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>87.99</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AQ240" t="inlineStr">
         <is>
-          <t>97.4384</t>
+          <t>95.6315</t>
         </is>
       </c>
       <c r="AR240" t="inlineStr">
         <is>
-          <t>0.3253</t>
+          <t>0.2023</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.0805</t>
         </is>
       </c>
       <c r="AT240" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.1736</t>
         </is>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>67.12</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.1253</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
